--- a/data/2026-05-05/BallparkPal_Pitchers.xlsx
+++ b/data/2026-05-05/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="96">
   <si>
     <t>GamePk</t>
   </si>
@@ -87,6 +87,222 @@
   </si>
   <si>
     <t>StolenBasesAllowed</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>6:45</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Bradley</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Cavalli</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Gausman</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Rasmussen</t>
+  </si>
+  <si>
+    <t>7:45</t>
+  </si>
+  <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>Pallante</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Brandon Sproat</t>
+  </si>
+  <si>
+    <t>Sproat</t>
+  </si>
+  <si>
+    <t>9:40</t>
+  </si>
+  <si>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Kirby</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Elder</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Cameron</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>Shohei Ohtani</t>
+  </si>
+  <si>
+    <t>Ohtani</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Lambert</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Valdez</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Brayan Bello</t>
+  </si>
+  <si>
+    <t>Bello</t>
+  </si>
+  <si>
+    <t>8:40</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Lorenzen</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Peralta</t>
+  </si>
+  <si>
+    <t>Jameson Taillon</t>
+  </si>
+  <si>
+    <t>Taillon</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Abbott</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
+  </si>
+  <si>
+    <t>ARI</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Chandler</t>
   </si>
 </sst>
 </file>
@@ -426,7 +642,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -501,6 +717,1486 @@
       </c>
       <c r="X1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2">
+        <v>822743</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>671737</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2">
+        <v>23.818</v>
+      </c>
+      <c r="L2">
+        <v>5.504</v>
+      </c>
+      <c r="M2">
+        <v>0.233</v>
+      </c>
+      <c r="N2">
+        <v>0.271</v>
+      </c>
+      <c r="O2">
+        <v>0.496</v>
+      </c>
+      <c r="P2">
+        <v>0.399</v>
+      </c>
+      <c r="Q2">
+        <v>14.974</v>
+      </c>
+      <c r="R2">
+        <v>28.767</v>
+      </c>
+      <c r="S2">
+        <v>2.707</v>
+      </c>
+      <c r="T2">
+        <v>5.18</v>
+      </c>
+      <c r="U2">
+        <v>5.792</v>
+      </c>
+      <c r="V2">
+        <v>2.358</v>
+      </c>
+      <c r="W2">
+        <v>0.794</v>
+      </c>
+      <c r="X2">
+        <v>0.448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3">
+        <v>822743</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>676917</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>21.727</v>
+      </c>
+      <c r="L3">
+        <v>4.889</v>
+      </c>
+      <c r="M3">
+        <v>0.203</v>
+      </c>
+      <c r="N3">
+        <v>0.336</v>
+      </c>
+      <c r="O3">
+        <v>0.461</v>
+      </c>
+      <c r="P3">
+        <v>0.234</v>
+      </c>
+      <c r="Q3">
+        <v>11.656</v>
+      </c>
+      <c r="R3">
+        <v>23.229</v>
+      </c>
+      <c r="S3">
+        <v>2.525</v>
+      </c>
+      <c r="T3">
+        <v>5.278</v>
+      </c>
+      <c r="U3">
+        <v>4.662</v>
+      </c>
+      <c r="V3">
+        <v>2.114</v>
+      </c>
+      <c r="W3">
+        <v>0.528</v>
+      </c>
+      <c r="X3">
+        <v>0.596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4">
+        <v>822986</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>592332</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4">
+        <v>22.776</v>
+      </c>
+      <c r="L4">
+        <v>5.599</v>
+      </c>
+      <c r="M4">
+        <v>0.217</v>
+      </c>
+      <c r="N4">
+        <v>0.329</v>
+      </c>
+      <c r="O4">
+        <v>0.453</v>
+      </c>
+      <c r="P4">
+        <v>0.455</v>
+      </c>
+      <c r="Q4">
+        <v>15.222</v>
+      </c>
+      <c r="R4">
+        <v>27.988</v>
+      </c>
+      <c r="S4">
+        <v>2.179</v>
+      </c>
+      <c r="T4">
+        <v>4.851</v>
+      </c>
+      <c r="U4">
+        <v>4.868</v>
+      </c>
+      <c r="V4">
+        <v>1.234</v>
+      </c>
+      <c r="W4">
+        <v>0.675</v>
+      </c>
+      <c r="X4">
+        <v>0.686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5">
+        <v>822986</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>656876</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5">
+        <v>22.977</v>
+      </c>
+      <c r="L5">
+        <v>5.743</v>
+      </c>
+      <c r="M5">
+        <v>0.298</v>
+      </c>
+      <c r="N5">
+        <v>0.298</v>
+      </c>
+      <c r="O5">
+        <v>0.404</v>
+      </c>
+      <c r="P5">
+        <v>0.461</v>
+      </c>
+      <c r="Q5">
+        <v>17.34</v>
+      </c>
+      <c r="R5">
+        <v>30.902</v>
+      </c>
+      <c r="S5">
+        <v>2.011</v>
+      </c>
+      <c r="T5">
+        <v>4.627</v>
+      </c>
+      <c r="U5">
+        <v>5.358</v>
+      </c>
+      <c r="V5">
+        <v>1.219</v>
+      </c>
+      <c r="W5">
+        <v>0.706</v>
+      </c>
+      <c r="X5">
+        <v>0.506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6">
+        <v>823062</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>669467</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6">
+        <v>23.329</v>
+      </c>
+      <c r="L6">
+        <v>5.521</v>
+      </c>
+      <c r="M6">
+        <v>0.301</v>
+      </c>
+      <c r="N6">
+        <v>0.311</v>
+      </c>
+      <c r="O6">
+        <v>0.388</v>
+      </c>
+      <c r="P6">
+        <v>0.41</v>
+      </c>
+      <c r="Q6">
+        <v>12.134</v>
+      </c>
+      <c r="R6">
+        <v>24.157</v>
+      </c>
+      <c r="S6">
+        <v>2.118</v>
+      </c>
+      <c r="T6">
+        <v>4.795</v>
+      </c>
+      <c r="U6">
+        <v>3.501</v>
+      </c>
+      <c r="V6">
+        <v>2.329</v>
+      </c>
+      <c r="W6">
+        <v>0.312</v>
+      </c>
+      <c r="X6">
+        <v>1.045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7">
+        <v>823062</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>687075</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7">
+        <v>21.693</v>
+      </c>
+      <c r="L7">
+        <v>4.961</v>
+      </c>
+      <c r="M7">
+        <v>0.182</v>
+      </c>
+      <c r="N7">
+        <v>0.332</v>
+      </c>
+      <c r="O7">
+        <v>0.486</v>
+      </c>
+      <c r="P7">
+        <v>0.264</v>
+      </c>
+      <c r="Q7">
+        <v>11.786</v>
+      </c>
+      <c r="R7">
+        <v>23.279</v>
+      </c>
+      <c r="S7">
+        <v>2.294</v>
+      </c>
+      <c r="T7">
+        <v>4.825</v>
+      </c>
+      <c r="U7">
+        <v>4.377</v>
+      </c>
+      <c r="V7">
+        <v>2.297</v>
+      </c>
+      <c r="W7">
+        <v>0.418</v>
+      </c>
+      <c r="X7">
+        <v>0.474</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8">
+        <v>823142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>669923</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8">
+        <v>24.685</v>
+      </c>
+      <c r="L8">
+        <v>6.235</v>
+      </c>
+      <c r="M8">
+        <v>0.399</v>
+      </c>
+      <c r="N8">
+        <v>0.255</v>
+      </c>
+      <c r="O8">
+        <v>0.347</v>
+      </c>
+      <c r="P8">
+        <v>0.6</v>
+      </c>
+      <c r="Q8">
+        <v>18.383</v>
+      </c>
+      <c r="R8">
+        <v>33.054</v>
+      </c>
+      <c r="S8">
+        <v>1.963</v>
+      </c>
+      <c r="T8">
+        <v>4.766</v>
+      </c>
+      <c r="U8">
+        <v>5.148</v>
+      </c>
+      <c r="V8">
+        <v>1.411</v>
+      </c>
+      <c r="W8">
+        <v>0.763</v>
+      </c>
+      <c r="X8">
+        <v>0.334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9">
+        <v>823142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9">
+        <v>693821</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9">
+        <v>23.893</v>
+      </c>
+      <c r="L9">
+        <v>5.707</v>
+      </c>
+      <c r="M9">
+        <v>0.193</v>
+      </c>
+      <c r="N9">
+        <v>0.418</v>
+      </c>
+      <c r="O9">
+        <v>0.389</v>
+      </c>
+      <c r="P9">
+        <v>0.48</v>
+      </c>
+      <c r="Q9">
+        <v>15.423</v>
+      </c>
+      <c r="R9">
+        <v>29.116</v>
+      </c>
+      <c r="S9">
+        <v>2.559</v>
+      </c>
+      <c r="T9">
+        <v>5.016</v>
+      </c>
+      <c r="U9">
+        <v>5.532</v>
+      </c>
+      <c r="V9">
+        <v>1.94</v>
+      </c>
+      <c r="W9">
+        <v>0.906</v>
+      </c>
+      <c r="X9">
+        <v>0.632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10">
+        <v>824119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>668909</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10">
+        <v>23.565</v>
+      </c>
+      <c r="L10">
+        <v>5.722</v>
+      </c>
+      <c r="M10">
+        <v>0.279</v>
+      </c>
+      <c r="N10">
+        <v>0.245</v>
+      </c>
+      <c r="O10">
+        <v>0.477</v>
+      </c>
+      <c r="P10">
+        <v>0.486</v>
+      </c>
+      <c r="Q10">
+        <v>17.012</v>
+      </c>
+      <c r="R10">
+        <v>31.204</v>
+      </c>
+      <c r="S10">
+        <v>2.292</v>
+      </c>
+      <c r="T10">
+        <v>4.603</v>
+      </c>
+      <c r="U10">
+        <v>5.766</v>
+      </c>
+      <c r="V10">
+        <v>1.967</v>
+      </c>
+      <c r="W10">
+        <v>0.75</v>
+      </c>
+      <c r="X10">
+        <v>0.475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11">
+        <v>824119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11">
+        <v>702070</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>23.505</v>
+      </c>
+      <c r="L11">
+        <v>5.372</v>
+      </c>
+      <c r="M11">
+        <v>0.219</v>
+      </c>
+      <c r="N11">
+        <v>0.421</v>
+      </c>
+      <c r="O11">
+        <v>0.36</v>
+      </c>
+      <c r="P11">
+        <v>0.368</v>
+      </c>
+      <c r="Q11">
+        <v>10.684</v>
+      </c>
+      <c r="R11">
+        <v>22.283</v>
+      </c>
+      <c r="S11">
+        <v>2.854</v>
+      </c>
+      <c r="T11">
+        <v>5.551</v>
+      </c>
+      <c r="U11">
+        <v>3.983</v>
+      </c>
+      <c r="V11">
+        <v>2.03</v>
+      </c>
+      <c r="W11">
+        <v>0.73</v>
+      </c>
+      <c r="X11">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12">
+        <v>824200</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12">
+        <v>660271</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12">
+        <v>23.083</v>
+      </c>
+      <c r="L12">
+        <v>5.591</v>
+      </c>
+      <c r="M12">
+        <v>0.274</v>
+      </c>
+      <c r="N12">
+        <v>0.219</v>
+      </c>
+      <c r="O12">
+        <v>0.507</v>
+      </c>
+      <c r="P12">
+        <v>0.454</v>
+      </c>
+      <c r="Q12">
+        <v>18.826</v>
+      </c>
+      <c r="R12">
+        <v>33.756</v>
+      </c>
+      <c r="S12">
+        <v>2.144</v>
+      </c>
+      <c r="T12">
+        <v>4.51</v>
+      </c>
+      <c r="U12">
+        <v>6.651</v>
+      </c>
+      <c r="V12">
+        <v>1.976</v>
+      </c>
+      <c r="W12">
+        <v>0.688</v>
+      </c>
+      <c r="X12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13">
+        <v>824200</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>663567</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13">
+        <v>19.222</v>
+      </c>
+      <c r="L13">
+        <v>4.382</v>
+      </c>
+      <c r="M13">
+        <v>0.121</v>
+      </c>
+      <c r="N13">
+        <v>0.376</v>
+      </c>
+      <c r="O13">
+        <v>0.503</v>
+      </c>
+      <c r="P13">
+        <v>0.096</v>
+      </c>
+      <c r="Q13">
+        <v>10.862</v>
+      </c>
+      <c r="R13">
+        <v>20.639</v>
+      </c>
+      <c r="S13">
+        <v>2.178</v>
+      </c>
+      <c r="T13">
+        <v>3.867</v>
+      </c>
+      <c r="U13">
+        <v>4.305</v>
+      </c>
+      <c r="V13">
+        <v>2.363</v>
+      </c>
+      <c r="W13">
+        <v>0.685</v>
+      </c>
+      <c r="X13">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14">
+        <v>824281</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>664285</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14">
+        <v>25.27</v>
+      </c>
+      <c r="L14">
+        <v>6.19</v>
+      </c>
+      <c r="M14">
+        <v>0.465</v>
+      </c>
+      <c r="N14">
+        <v>0.206</v>
+      </c>
+      <c r="O14">
+        <v>0.329</v>
+      </c>
+      <c r="P14">
+        <v>0.596</v>
+      </c>
+      <c r="Q14">
+        <v>16.33</v>
+      </c>
+      <c r="R14">
+        <v>30.837</v>
+      </c>
+      <c r="S14">
+        <v>2.036</v>
+      </c>
+      <c r="T14">
+        <v>4.917</v>
+      </c>
+      <c r="U14">
+        <v>4.401</v>
+      </c>
+      <c r="V14">
+        <v>2.186</v>
+      </c>
+      <c r="W14">
+        <v>0.316</v>
+      </c>
+      <c r="X14">
+        <v>0.664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15">
+        <v>824281</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>678394</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15">
+        <v>21.029</v>
+      </c>
+      <c r="L15">
+        <v>4.624</v>
+      </c>
+      <c r="M15">
+        <v>0.104</v>
+      </c>
+      <c r="N15">
+        <v>0.469</v>
+      </c>
+      <c r="O15">
+        <v>0.427</v>
+      </c>
+      <c r="P15">
+        <v>0.161</v>
+      </c>
+      <c r="Q15">
+        <v>5.336</v>
+      </c>
+      <c r="R15">
+        <v>13.705</v>
+      </c>
+      <c r="S15">
+        <v>2.791</v>
+      </c>
+      <c r="T15">
+        <v>5.032</v>
+      </c>
+      <c r="U15">
+        <v>2.313</v>
+      </c>
+      <c r="V15">
+        <v>2.515</v>
+      </c>
+      <c r="W15">
+        <v>0.567</v>
+      </c>
+      <c r="X15">
+        <v>0.263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16">
+        <v>824362</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16">
+        <v>547179</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16">
+        <v>23.01</v>
+      </c>
+      <c r="L16">
+        <v>5.037</v>
+      </c>
+      <c r="M16">
+        <v>0.214</v>
+      </c>
+      <c r="N16">
+        <v>0.385</v>
+      </c>
+      <c r="O16">
+        <v>0.4</v>
+      </c>
+      <c r="P16">
+        <v>0.251</v>
+      </c>
+      <c r="Q16">
+        <v>7.105</v>
+      </c>
+      <c r="R16">
+        <v>17.089</v>
+      </c>
+      <c r="S16">
+        <v>3.371</v>
+      </c>
+      <c r="T16">
+        <v>6.305</v>
+      </c>
+      <c r="U16">
+        <v>3.268</v>
+      </c>
+      <c r="V16">
+        <v>1.835</v>
+      </c>
+      <c r="W16">
+        <v>0.779</v>
+      </c>
+      <c r="X16">
+        <v>0.403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>824362</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17">
+        <v>642547</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17">
+        <v>22.291</v>
+      </c>
+      <c r="L17">
+        <v>5.039</v>
+      </c>
+      <c r="M17">
+        <v>0.2</v>
+      </c>
+      <c r="N17">
+        <v>0.253</v>
+      </c>
+      <c r="O17">
+        <v>0.547</v>
+      </c>
+      <c r="P17">
+        <v>0.264</v>
+      </c>
+      <c r="Q17">
+        <v>11.942</v>
+      </c>
+      <c r="R17">
+        <v>23.68</v>
+      </c>
+      <c r="S17">
+        <v>2.959</v>
+      </c>
+      <c r="T17">
+        <v>5.42</v>
+      </c>
+      <c r="U17">
+        <v>5.062</v>
+      </c>
+      <c r="V17">
+        <v>1.926</v>
+      </c>
+      <c r="W17">
+        <v>0.822</v>
+      </c>
+      <c r="X17">
+        <v>0.385</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>824682</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18">
+        <v>592791</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18">
+        <v>23.892</v>
+      </c>
+      <c r="L18">
+        <v>5.96</v>
+      </c>
+      <c r="M18">
+        <v>0.497</v>
+      </c>
+      <c r="N18">
+        <v>0.166</v>
+      </c>
+      <c r="O18">
+        <v>0.336</v>
+      </c>
+      <c r="P18">
+        <v>0.536</v>
+      </c>
+      <c r="Q18">
+        <v>19.598</v>
+      </c>
+      <c r="R18">
+        <v>34.654</v>
+      </c>
+      <c r="S18">
+        <v>1.955</v>
+      </c>
+      <c r="T18">
+        <v>4.031</v>
+      </c>
+      <c r="U18">
+        <v>5.837</v>
+      </c>
+      <c r="V18">
+        <v>2.006</v>
+      </c>
+      <c r="W18">
+        <v>0.716</v>
+      </c>
+      <c r="X18">
+        <v>0.589</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
+        <v>824682</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19">
+        <v>671096</v>
+      </c>
+      <c r="E19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19">
+        <v>21.33</v>
+      </c>
+      <c r="L19">
+        <v>4.608</v>
+      </c>
+      <c r="M19">
+        <v>0.091</v>
+      </c>
+      <c r="N19">
+        <v>0.516</v>
+      </c>
+      <c r="O19">
+        <v>0.393</v>
+      </c>
+      <c r="P19">
+        <v>0.171</v>
+      </c>
+      <c r="Q19">
+        <v>5.51</v>
+      </c>
+      <c r="R19">
+        <v>14.198</v>
+      </c>
+      <c r="S19">
+        <v>3.166</v>
+      </c>
+      <c r="T19">
+        <v>5.65</v>
+      </c>
+      <c r="U19">
+        <v>2.881</v>
+      </c>
+      <c r="V19">
+        <v>2.104</v>
+      </c>
+      <c r="W19">
+        <v>0.721</v>
+      </c>
+      <c r="X19">
+        <v>0.663</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>825092</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>593958</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20">
+        <v>23.708</v>
+      </c>
+      <c r="L20">
+        <v>5.446</v>
+      </c>
+      <c r="M20">
+        <v>0.239</v>
+      </c>
+      <c r="N20">
+        <v>0.361</v>
+      </c>
+      <c r="O20">
+        <v>0.4</v>
+      </c>
+      <c r="P20">
+        <v>0.371</v>
+      </c>
+      <c r="Q20">
+        <v>11.78</v>
+      </c>
+      <c r="R20">
+        <v>23.895</v>
+      </c>
+      <c r="S20">
+        <v>2.722</v>
+      </c>
+      <c r="T20">
+        <v>5.449</v>
+      </c>
+      <c r="U20">
+        <v>4.269</v>
+      </c>
+      <c r="V20">
+        <v>2.113</v>
+      </c>
+      <c r="W20">
+        <v>0.616</v>
+      </c>
+      <c r="X20">
+        <v>0.515</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
+        <v>825092</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21">
+        <v>696149</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" t="s">
+        <v>92</v>
+      </c>
+      <c r="K21">
+        <v>21.427</v>
+      </c>
+      <c r="L21">
+        <v>5.067</v>
+      </c>
+      <c r="M21">
+        <v>0.202</v>
+      </c>
+      <c r="N21">
+        <v>0.248</v>
+      </c>
+      <c r="O21">
+        <v>0.55</v>
+      </c>
+      <c r="P21">
+        <v>0.285</v>
+      </c>
+      <c r="Q21">
+        <v>12.793</v>
+      </c>
+      <c r="R21">
+        <v>24.18</v>
+      </c>
+      <c r="S21">
+        <v>2.008</v>
+      </c>
+      <c r="T21">
+        <v>3.98</v>
+      </c>
+      <c r="U21">
+        <v>4.216</v>
+      </c>
+      <c r="V21">
+        <v>2.418</v>
+      </c>
+      <c r="W21">
+        <v>0.488</v>
+      </c>
+      <c r="X21">
+        <v>0.392</v>
       </c>
     </row>
   </sheetData>
